--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AY256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -24848,7 +24848,7 @@
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -26577,10 +26577,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135358529</v>
+        <v>135435470</v>
       </c>
       <c r="B234" t="n">
-        <v>58079</v>
+        <v>58136</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26588,37 +26588,41 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>657920</v>
+        <v>657931</v>
       </c>
       <c r="R234" t="n">
-        <v>7328326</v>
+        <v>7328314</v>
       </c>
       <c r="S234" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26647,7 +26651,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26657,12 +26661,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>16:17</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>3st</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26677,12 +26676,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -26693,7 +26692,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135362228</v>
+        <v>135358529</v>
       </c>
       <c r="B235" t="n">
         <v>58079</v>
@@ -26722,23 +26721,19 @@
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>657944</v>
+        <v>657920</v>
       </c>
       <c r="R235" t="n">
-        <v>7328343</v>
+        <v>7328326</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26767,7 +26762,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26777,7 +26772,12 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26792,12 +26792,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -26808,27 +26808,27 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135358864</v>
+        <v>135362228</v>
       </c>
       <c r="B236" t="n">
-        <v>5201</v>
+        <v>58079</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -26837,19 +26837,23 @@
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>658134</v>
+        <v>657944</v>
       </c>
       <c r="R236" t="n">
-        <v>7328300</v>
+        <v>7328343</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26878,7 +26882,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26888,7 +26892,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26903,12 +26907,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26919,60 +26923,48 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135357260</v>
+        <v>135358864</v>
       </c>
       <c r="B237" t="n">
-        <v>99195</v>
+        <v>5201</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>657949</v>
+        <v>658134</v>
       </c>
       <c r="R237" t="n">
-        <v>7328433</v>
+        <v>7328300</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -27001,7 +26993,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -27011,12 +27003,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>8 stänglar</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27025,19 +27012,18 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27048,7 +27034,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135363836</v>
+        <v>135357260</v>
       </c>
       <c r="B238" t="n">
         <v>99195</v>
@@ -27076,17 +27062,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>658130</v>
+        <v>657949</v>
       </c>
       <c r="R238" t="n">
-        <v>7328226</v>
+        <v>7328433</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -27118,7 +27116,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27128,12 +27126,12 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Ca. 100 blommande skott.</t>
+          <t>8 stänglar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27142,18 +27140,19 @@
       <c r="AE238" t="b">
         <v>0</v>
       </c>
+      <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -27164,48 +27163,48 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135357535</v>
+        <v>135363836</v>
       </c>
       <c r="B239" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>658001</v>
+        <v>658130</v>
       </c>
       <c r="R239" t="n">
-        <v>7328390</v>
+        <v>7328226</v>
       </c>
       <c r="S239" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27234,7 +27233,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27244,7 +27243,12 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Ca. 100 blommande skott.</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27259,12 +27263,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -27275,7 +27279,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135358514</v>
+        <v>135357535</v>
       </c>
       <c r="B240" t="n">
         <v>106309</v>
@@ -27306,17 +27310,17 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>658129</v>
+        <v>658001</v>
       </c>
       <c r="R240" t="n">
-        <v>7328219</v>
+        <v>7328390</v>
       </c>
       <c r="S240" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27345,7 +27349,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27355,7 +27359,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27370,12 +27374,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -27386,7 +27390,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135358537</v>
+        <v>135358514</v>
       </c>
       <c r="B241" t="n">
         <v>106309</v>
@@ -27421,13 +27425,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>657761</v>
+        <v>658129</v>
       </c>
       <c r="R241" t="n">
-        <v>7328385</v>
+        <v>7328219</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -27456,7 +27460,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27466,7 +27470,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27497,7 +27501,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135363837</v>
+        <v>135358537</v>
       </c>
       <c r="B242" t="n">
         <v>106309</v>
@@ -27532,10 +27536,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>658130</v>
+        <v>657761</v>
       </c>
       <c r="R242" t="n">
-        <v>7328226</v>
+        <v>7328385</v>
       </c>
       <c r="S242" t="n">
         <v>5</v>
@@ -27567,7 +27571,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27577,7 +27581,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27592,12 +27596,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27608,7 +27612,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135363840</v>
+        <v>135363837</v>
       </c>
       <c r="B243" t="n">
         <v>106309</v>
@@ -27643,10 +27647,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>658044</v>
+        <v>658130</v>
       </c>
       <c r="R243" t="n">
-        <v>7328239</v>
+        <v>7328226</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -27678,7 +27682,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27688,7 +27692,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27708,7 +27712,7 @@
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -27719,10 +27723,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135358540</v>
+        <v>135363840</v>
       </c>
       <c r="B244" t="n">
-        <v>98066</v>
+        <v>106309</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27730,21 +27734,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27754,13 +27758,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>657728</v>
+        <v>658044</v>
       </c>
       <c r="R244" t="n">
-        <v>7328365</v>
+        <v>7328239</v>
       </c>
       <c r="S244" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27789,7 +27793,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27799,7 +27803,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27814,12 +27818,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27830,10 +27834,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135357257</v>
+        <v>135358540</v>
       </c>
       <c r="B245" t="n">
-        <v>99217</v>
+        <v>98066</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27841,21 +27845,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27865,13 +27869,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>657988</v>
+        <v>657728</v>
       </c>
       <c r="R245" t="n">
-        <v>7328384</v>
+        <v>7328365</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27900,7 +27904,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27910,7 +27914,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27925,12 +27929,12 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -27941,7 +27945,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135357530</v>
+        <v>135357257</v>
       </c>
       <c r="B246" t="n">
         <v>99217</v>
@@ -27972,14 +27976,14 @@
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>657995</v>
+        <v>657988</v>
       </c>
       <c r="R246" t="n">
-        <v>7328356</v>
+        <v>7328384</v>
       </c>
       <c r="S246" t="n">
         <v>5</v>
@@ -28011,7 +28015,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -28021,12 +28025,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>Elin G</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28041,12 +28040,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -28057,7 +28056,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135358927</v>
+        <v>135357530</v>
       </c>
       <c r="B247" t="n">
         <v>99217</v>
@@ -28088,14 +28087,14 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>657781</v>
+        <v>657995</v>
       </c>
       <c r="R247" t="n">
-        <v>7328332</v>
+        <v>7328356</v>
       </c>
       <c r="S247" t="n">
         <v>5</v>
@@ -28127,7 +28126,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28137,7 +28136,12 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Elin G</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28152,12 +28156,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -28168,7 +28172,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135362203</v>
+        <v>135358927</v>
       </c>
       <c r="B248" t="n">
         <v>99217</v>
@@ -28203,10 +28207,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>658187</v>
+        <v>657781</v>
       </c>
       <c r="R248" t="n">
-        <v>7328201</v>
+        <v>7328332</v>
       </c>
       <c r="S248" t="n">
         <v>5</v>
@@ -28238,7 +28242,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28248,7 +28252,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28263,12 +28267,12 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Linda Nordström, Elin Götmark</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -28279,7 +28283,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135362223</v>
+        <v>135362203</v>
       </c>
       <c r="B249" t="n">
         <v>99217</v>
@@ -28314,10 +28318,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>658012</v>
+        <v>658187</v>
       </c>
       <c r="R249" t="n">
-        <v>7328314</v>
+        <v>7328201</v>
       </c>
       <c r="S249" t="n">
         <v>5</v>
@@ -28349,7 +28353,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28359,7 +28363,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28390,7 +28394,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135363849</v>
+        <v>135362223</v>
       </c>
       <c r="B250" t="n">
         <v>99217</v>
@@ -28425,10 +28429,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>657813</v>
+        <v>658012</v>
       </c>
       <c r="R250" t="n">
-        <v>7328352</v>
+        <v>7328314</v>
       </c>
       <c r="S250" t="n">
         <v>5</v>
@@ -28460,7 +28464,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28470,7 +28474,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28485,12 +28489,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -28501,7 +28505,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135363851</v>
+        <v>135363849</v>
       </c>
       <c r="B251" t="n">
         <v>99217</v>
@@ -28536,10 +28540,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>657575</v>
+        <v>657813</v>
       </c>
       <c r="R251" t="n">
-        <v>7328321</v>
+        <v>7328352</v>
       </c>
       <c r="S251" t="n">
         <v>5</v>
@@ -28571,7 +28575,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28581,7 +28585,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28601,7 +28605,7 @@
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -28612,10 +28616,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135357533</v>
+        <v>135363851</v>
       </c>
       <c r="B252" t="n">
-        <v>100806</v>
+        <v>99217</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28623,34 +28627,34 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>222584</v>
+        <v>221952</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Svanvik_topo, Pi lm</t>
+          <t>Svanvik, Pi lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>657997</v>
+        <v>657575</v>
       </c>
       <c r="R252" t="n">
-        <v>7328373</v>
+        <v>7328321</v>
       </c>
       <c r="S252" t="n">
         <v>5</v>
@@ -28682,7 +28686,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28692,7 +28696,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28707,12 +28711,12 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Katharina Radloff, Elin Götmark</t>
+          <t>Klas Magnusson, Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -28723,7 +28727,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135358926</v>
+        <v>135357533</v>
       </c>
       <c r="B253" t="n">
         <v>100806</v>
@@ -28754,17 +28758,17 @@
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Svanvik, Pi lm</t>
+          <t>Svanvik_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>657781</v>
+        <v>657997</v>
       </c>
       <c r="R253" t="n">
-        <v>7328326</v>
+        <v>7328373</v>
       </c>
       <c r="S253" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -28793,7 +28797,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28803,7 +28807,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28818,12 +28822,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Linda Nordström, Elin Götmark</t>
+          <t>Katharina Radloff, Elin Götmark</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28834,32 +28838,32 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135358920</v>
+        <v>135358926</v>
       </c>
       <c r="B254" t="n">
-        <v>79963</v>
+        <v>100806</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>229821</v>
+        <v>222584</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28869,13 +28873,13 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>657852</v>
+        <v>657781</v>
       </c>
       <c r="R254" t="n">
-        <v>7328299</v>
+        <v>7328326</v>
       </c>
       <c r="S254" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -28904,7 +28908,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28914,7 +28918,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28945,32 +28949,32 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135358863</v>
+        <v>135358920</v>
       </c>
       <c r="B255" t="n">
-        <v>95840</v>
+        <v>79963</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1004672</v>
+        <v>229821</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28980,10 +28984,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>658147</v>
+        <v>657852</v>
       </c>
       <c r="R255" t="n">
-        <v>7328286</v>
+        <v>7328299</v>
       </c>
       <c r="S255" t="n">
         <v>5</v>
@@ -29015,7 +29019,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -29025,7 +29029,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29049,6 +29053,117 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>135358863</v>
+      </c>
+      <c r="B256" t="n">
+        <v>95840</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1004672</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Källmossor</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Philonotis</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Brid.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Svanvik, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>658147</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7328286</v>
+      </c>
+      <c r="S256" t="n">
+        <v>5</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Linda Nordström, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1856,6 +1856,9 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
@@ -1916,6 +1919,7 @@
       <c r="AE12" t="b">
         <v>1</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1930,7 +1934,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22701,6 +22709,9 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Svanvik, Pi lm</t>
@@ -22761,6 +22772,7 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22775,7 +22787,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY200" t="inlineStr"/>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -29723,14 +29739,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr"/>
@@ -29744,7 +29755,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY261" t="inlineStr"/>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY262"/>
+  <dimension ref="A1:AZ262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358925</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363850</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357527</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357538</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362202</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356943</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,6 +1874,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357830</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135520047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356953</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357254</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2272,6 +2342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357258</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2383,6 +2458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357261</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2494,6 +2574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357540</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2610,6 +2695,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357543</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2717,6 +2807,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357825</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2824,6 +2919,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357837</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2931,6 +3031,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357842</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3042,6 +3147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358539</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3153,6 +3263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358870</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3264,6 +3379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358879</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3375,6 +3495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358883</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3486,6 +3611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358885</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3597,6 +3727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358923</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3713,6 +3848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362243</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3825,6 +3965,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369274</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3951,6 +4096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363841</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4060,6 +4210,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356944</t>
         </is>
       </c>
     </row>
@@ -4182,6 +4337,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357526</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4293,6 +4453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357529</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4404,6 +4569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358523</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4515,6 +4685,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358526</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4626,6 +4801,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358531</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4737,6 +4917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358534</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4848,6 +5033,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358859</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4959,6 +5149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358869</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5070,6 +5265,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358874</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5181,6 +5381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358887</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5292,6 +5497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358906</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5403,6 +5613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358908</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5514,6 +5729,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358915</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5625,6 +5845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358917</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5736,6 +5961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362199</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5847,6 +6077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362242</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5959,6 +6194,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369261</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6071,6 +6311,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369262</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6183,6 +6428,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369267</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6291,6 +6541,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357838</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6388,6 +6643,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135312324</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6495,6 +6755,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357823</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6602,6 +6867,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357835</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6713,6 +6983,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358881</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6829,6 +7104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362216</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6940,6 +7220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357255</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7047,6 +7332,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357828</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7158,6 +7448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358867</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7269,6 +7564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358919</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7380,6 +7680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358922</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7491,6 +7796,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362204</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7602,6 +7912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356949</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7709,6 +8024,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357827</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7816,6 +8136,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357831</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7923,6 +8248,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357844</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8030,6 +8360,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357846</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8156,6 +8491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363847</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8267,6 +8607,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357241</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8378,6 +8723,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357252</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8489,6 +8839,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358860</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8605,6 +8960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358872</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8716,6 +9076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358900</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8827,6 +9192,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358902</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8938,6 +9308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358911</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9049,6 +9424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358913</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9165,6 +9545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362200</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9277,6 +9662,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369260</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9389,6 +9779,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369263</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9501,6 +9896,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369264</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9612,6 +10012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357536</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9720,6 +10125,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357826</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9840,6 +10250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357246</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9951,6 +10366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358513</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10063,6 +10483,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369275</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10174,6 +10599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357539</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10285,6 +10715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435690</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10396,6 +10831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435692</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10507,6 +10947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356945</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10618,6 +11063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356947</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10729,6 +11179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356932</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10840,6 +11295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356933</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10951,6 +11411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356936</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11062,6 +11527,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356938</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11173,6 +11643,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356939</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11284,6 +11759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356940</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11395,6 +11875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356941</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11506,6 +11991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356946</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11617,6 +12107,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356948</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11728,6 +12223,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356951</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11839,6 +12339,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356952</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11950,6 +12455,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357242</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12061,6 +12571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357243</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12172,6 +12687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357245</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12283,6 +12803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357250</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12394,6 +12919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357251</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12505,6 +13035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357253</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12616,6 +13151,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357259</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12727,6 +13267,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357262</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12838,6 +13383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357521</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12949,6 +13499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357522</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13060,6 +13615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357528</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13171,6 +13731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357537</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13282,6 +13847,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357546</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13393,6 +13963,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357547</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13500,6 +14075,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357833</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13612,6 +14192,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357834</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13719,6 +14304,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357836</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13831,6 +14421,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357839</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13932,6 +14527,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358229</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14033,6 +14633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358230</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14134,6 +14739,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358232</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14235,6 +14845,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358233</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14336,6 +14951,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358234</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14447,6 +15067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358505</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14558,6 +15183,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358506</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14669,6 +15299,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358507</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14780,6 +15415,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358508</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14891,6 +15531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358509</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15002,6 +15647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358510</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15113,6 +15763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358515</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15224,6 +15879,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358519</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15340,6 +16000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358521</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15451,6 +16116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358525</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15562,6 +16232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358532</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15673,6 +16348,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358533</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15784,6 +16464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358536</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15895,6 +16580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358538</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16006,6 +16696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358858</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16117,6 +16812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358861</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16228,6 +16928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358866</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16339,6 +17044,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358871</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16450,6 +17160,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358877</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16561,6 +17276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358904</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16672,6 +17392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358909</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16783,6 +17508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358912</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16894,6 +17624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358914</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17005,6 +17740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358918</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17116,6 +17856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358924</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17227,6 +17972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362196</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17338,6 +18088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362197</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17449,6 +18204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362198</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17560,6 +18320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362201</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17671,6 +18436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362205</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17782,6 +18552,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362206</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17893,6 +18668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362207</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18004,6 +18784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362209</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18115,6 +18900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362210</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18226,6 +19016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362213</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18337,6 +19132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362215</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18448,6 +19248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362218</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18559,6 +19364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362219</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18670,6 +19480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362220</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18781,6 +19596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362221</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18892,6 +19712,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362224</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19003,6 +19828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362225</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19114,6 +19944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362226</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19225,6 +20060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362227</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19336,6 +20176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362230</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19447,6 +20292,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362231</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19558,6 +20408,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362232</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19669,6 +20524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362233</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19780,6 +20640,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362235</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19891,6 +20756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362236</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20002,6 +20872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362237</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20113,6 +20988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362238</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20224,6 +21104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362239</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20335,6 +21220,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362240</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20446,6 +21336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362241</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20557,6 +21452,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362244</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20668,6 +21568,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362245</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20779,6 +21684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362246</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20890,6 +21800,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362247</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21001,6 +21916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363842</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21112,6 +22032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363846</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21224,6 +22149,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369259</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21336,6 +22266,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369266</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21448,6 +22383,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369273</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21560,6 +22500,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369277</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21672,6 +22617,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369278</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21783,6 +22733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357524</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21894,6 +22849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358910</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22005,6 +22965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356934</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22116,6 +23081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356935</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22227,6 +23197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356950</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22338,6 +23313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357244</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22454,6 +23434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357523</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22565,6 +23550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358862</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22677,6 +23667,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369265</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22792,6 +23787,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521443</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22903,6 +23903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358512</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23014,6 +24019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358890</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23125,6 +24135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358896</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23236,6 +24251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358898</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23362,6 +24382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363839</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23488,6 +24513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363843</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23614,6 +24644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363845</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23726,6 +24761,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369268</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23838,6 +24878,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369271</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23950,6 +24995,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369280</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24061,6 +25111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357249</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24172,6 +25227,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358520</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24283,6 +25343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358894</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24395,6 +25460,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369269</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24506,6 +25576,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357247</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24622,6 +25697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358516</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24733,6 +25813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358868</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24844,6 +25929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358889</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24955,6 +26045,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358892</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25071,6 +26166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362208</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25182,6 +26282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362212</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25308,6 +26413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363838</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25434,6 +26544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363844</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25546,6 +26661,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369270</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25663,6 +26783,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357824</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25780,6 +26905,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357829</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25897,6 +27027,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357841</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26014,6 +27149,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357843</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26131,6 +27271,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357845</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26247,6 +27392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358857</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26363,6 +27513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358865</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26475,6 +27630,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135369279</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26586,6 +27746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358873</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26693,6 +27858,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357847</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26804,6 +27974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358530</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26915,6 +28090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358916</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27026,6 +28206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358921</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27141,6 +28326,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435470</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27255,6 +28445,11 @@
       <c r="AY239" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358529</t>
         </is>
       </c>
     </row>
@@ -27372,6 +28567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362228</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27483,6 +28683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358864</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27604,6 +28809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135435699</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27733,6 +28943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357260</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27849,6 +29064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363836</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27960,6 +29180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357535</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28071,6 +29296,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358514</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28182,6 +29412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358537</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28293,6 +29528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363837</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28404,6 +29644,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363840</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28515,6 +29760,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358540</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28626,6 +29876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357257</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28742,6 +29997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357530</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28853,6 +30113,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358927</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28964,6 +30229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362203</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29075,6 +30345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362223</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29186,6 +30461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363849</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29297,6 +30577,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363851</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29408,6 +30693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357533</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29519,6 +30809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358926</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29628,6 +30923,11 @@
       <c r="AY260" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358920</t>
         </is>
       </c>
     </row>
@@ -29760,6 +31060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521161</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29871,8 +31176,276 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358863</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Paulina Delin, Linda Nordström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -23663,7 +23663,7 @@
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -24757,7 +24757,7 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
+          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135358925</v>
       </c>
       <c r="B2" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135363850</v>
       </c>
       <c r="B3" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135357256</v>
       </c>
       <c r="B4" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135357527</v>
       </c>
       <c r="B5" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135357531</v>
       </c>
       <c r="B6" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>135357538</v>
       </c>
       <c r="B7" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>135363848</v>
       </c>
       <c r="B8" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135362202</v>
       </c>
       <c r="B9" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135356943</v>
       </c>
       <c r="B10" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>135357830</v>
       </c>
       <c r="B11" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135520047</v>
       </c>
       <c r="B12" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135356953</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135357254</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135357258</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135357261</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>135357540</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>135357543</v>
       </c>
       <c r="B18" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>135357825</v>
       </c>
       <c r="B19" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135357837</v>
       </c>
       <c r="B20" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>135357842</v>
       </c>
       <c r="B21" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135358539</v>
       </c>
       <c r="B22" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135358870</v>
       </c>
       <c r="B23" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135358879</v>
       </c>
       <c r="B24" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135358883</v>
       </c>
       <c r="B25" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135358885</v>
       </c>
       <c r="B26" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135358923</v>
       </c>
       <c r="B27" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135362243</v>
       </c>
       <c r="B28" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>135369274</v>
       </c>
       <c r="B29" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>135363841</v>
       </c>
       <c r="B30" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135356944</v>
       </c>
       <c r="B31" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>135357526</v>
       </c>
       <c r="B32" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>135357529</v>
       </c>
       <c r="B33" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>135358523</v>
       </c>
       <c r="B34" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>135358526</v>
       </c>
       <c r="B35" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>135358531</v>
       </c>
       <c r="B36" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>135358534</v>
       </c>
       <c r="B37" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>135358859</v>
       </c>
       <c r="B38" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>135358869</v>
       </c>
       <c r="B39" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>135358874</v>
       </c>
       <c r="B40" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>135358887</v>
       </c>
       <c r="B41" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135358906</v>
       </c>
       <c r="B42" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135358908</v>
       </c>
       <c r="B43" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135358915</v>
       </c>
       <c r="B44" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>135358917</v>
       </c>
       <c r="B45" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>135362199</v>
       </c>
       <c r="B46" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>135362242</v>
       </c>
       <c r="B47" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>135369261</v>
       </c>
       <c r="B48" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Paulina Delin, Linda Nordström</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
         <v>135369262</v>
       </c>
       <c r="B49" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>135369267</v>
       </c>
       <c r="B50" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>135357838</v>
       </c>
       <c r="B51" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>135312324</v>
       </c>
       <c r="B52" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>135357823</v>
       </c>
       <c r="B53" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>135357835</v>
       </c>
       <c r="B54" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>135358881</v>
       </c>
       <c r="B55" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>135362216</v>
       </c>
       <c r="B56" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>135357255</v>
       </c>
       <c r="B57" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>135357828</v>
       </c>
       <c r="B58" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>135358867</v>
       </c>
       <c r="B59" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>135358919</v>
       </c>
       <c r="B60" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135358922</v>
       </c>
       <c r="B61" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>135362204</v>
       </c>
       <c r="B62" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>135356949</v>
       </c>
       <c r="B63" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135357827</v>
       </c>
       <c r="B64" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>135357831</v>
       </c>
       <c r="B65" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135357844</v>
       </c>
       <c r="B66" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>135357846</v>
       </c>
       <c r="B67" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135363847</v>
       </c>
       <c r="B68" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135357241</v>
       </c>
       <c r="B69" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>135357252</v>
       </c>
       <c r="B70" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>135358860</v>
       </c>
       <c r="B71" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>135358872</v>
       </c>
       <c r="B72" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135358900</v>
       </c>
       <c r="B73" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>135358902</v>
       </c>
       <c r="B74" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>135358911</v>
       </c>
       <c r="B75" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>135358913</v>
       </c>
       <c r="B76" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>135362200</v>
       </c>
       <c r="B77" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>135369260</v>
       </c>
       <c r="B78" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>135369263</v>
       </c>
       <c r="B79" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>135369264</v>
       </c>
       <c r="B80" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9907,7 +9907,7 @@
         <v>135357536</v>
       </c>
       <c r="B81" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135357826</v>
       </c>
       <c r="B82" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>135357246</v>
       </c>
       <c r="B83" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>135358513</v>
       </c>
       <c r="B84" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>135369275</v>
       </c>
       <c r="B85" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
         <v>135357539</v>
       </c>
       <c r="B86" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>135435690</v>
       </c>
       <c r="B87" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135435692</v>
       </c>
       <c r="B88" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>135356945</v>
       </c>
       <c r="B89" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>135356947</v>
       </c>
       <c r="B90" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>135356932</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>135356933</v>
       </c>
       <c r="B92" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>135356936</v>
       </c>
       <c r="B93" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>135356938</v>
       </c>
       <c r="B94" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>135356939</v>
       </c>
       <c r="B95" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>135356940</v>
       </c>
       <c r="B96" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>135356941</v>
       </c>
       <c r="B97" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>135356946</v>
       </c>
       <c r="B98" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>135356948</v>
       </c>
       <c r="B99" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>135356951</v>
       </c>
       <c r="B100" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>135356952</v>
       </c>
       <c r="B101" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>135357242</v>
       </c>
       <c r="B102" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>135357243</v>
       </c>
       <c r="B103" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>135357245</v>
       </c>
       <c r="B104" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>135357250</v>
       </c>
       <c r="B105" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>135357251</v>
       </c>
       <c r="B106" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>135357253</v>
       </c>
       <c r="B107" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>135357259</v>
       </c>
       <c r="B108" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>135357262</v>
       </c>
       <c r="B109" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>135357521</v>
       </c>
       <c r="B110" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>135357522</v>
       </c>
       <c r="B111" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>135357528</v>
       </c>
       <c r="B112" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>135357537</v>
       </c>
       <c r="B113" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>135357546</v>
       </c>
       <c r="B114" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>135357547</v>
       </c>
       <c r="B115" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>135357833</v>
       </c>
       <c r="B116" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>135357834</v>
       </c>
       <c r="B117" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>135357836</v>
       </c>
       <c r="B118" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>135357839</v>
       </c>
       <c r="B119" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>135358229</v>
       </c>
       <c r="B120" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>135358230</v>
       </c>
       <c r="B121" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>135358232</v>
       </c>
       <c r="B122" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>135358233</v>
       </c>
       <c r="B123" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>135358234</v>
       </c>
       <c r="B124" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>135358505</v>
       </c>
       <c r="B125" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>135358506</v>
       </c>
       <c r="B126" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>135358507</v>
       </c>
       <c r="B127" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>135358508</v>
       </c>
       <c r="B128" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>135358509</v>
       </c>
       <c r="B129" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>135358510</v>
       </c>
       <c r="B130" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>135358515</v>
       </c>
       <c r="B131" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>135358519</v>
       </c>
       <c r="B132" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>135358521</v>
       </c>
       <c r="B133" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>135358525</v>
       </c>
       <c r="B134" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>135358532</v>
       </c>
       <c r="B135" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>135358533</v>
       </c>
       <c r="B136" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>135358536</v>
       </c>
       <c r="B137" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>135358538</v>
       </c>
       <c r="B138" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>135358858</v>
       </c>
       <c r="B139" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>135358861</v>
       </c>
       <c r="B140" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>135358866</v>
       </c>
       <c r="B141" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>135358871</v>
       </c>
       <c r="B142" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>135358877</v>
       </c>
       <c r="B143" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>135358904</v>
       </c>
       <c r="B144" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>135358909</v>
       </c>
       <c r="B145" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>135358912</v>
       </c>
       <c r="B146" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>135358914</v>
       </c>
       <c r="B147" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>135358918</v>
       </c>
       <c r="B148" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>135358924</v>
       </c>
       <c r="B149" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>135362196</v>
       </c>
       <c r="B150" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>135362197</v>
       </c>
       <c r="B151" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>135362198</v>
       </c>
       <c r="B152" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>135362201</v>
       </c>
       <c r="B153" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>135362205</v>
       </c>
       <c r="B154" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>135362206</v>
       </c>
       <c r="B155" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>135362207</v>
       </c>
       <c r="B156" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         <v>135362209</v>
       </c>
       <c r="B157" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>135362210</v>
       </c>
       <c r="B158" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>135362213</v>
       </c>
       <c r="B159" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>135362215</v>
       </c>
       <c r="B160" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>135362218</v>
       </c>
       <c r="B161" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>135362219</v>
       </c>
       <c r="B162" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>135362220</v>
       </c>
       <c r="B163" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>135362221</v>
       </c>
       <c r="B164" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>135362224</v>
       </c>
       <c r="B165" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>135362225</v>
       </c>
       <c r="B166" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>135362226</v>
       </c>
       <c r="B167" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>135362227</v>
       </c>
       <c r="B168" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>135362230</v>
       </c>
       <c r="B169" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>135362231</v>
       </c>
       <c r="B170" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>135362232</v>
       </c>
       <c r="B171" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>135362233</v>
       </c>
       <c r="B172" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>135362235</v>
       </c>
       <c r="B173" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>135362236</v>
       </c>
       <c r="B174" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>135362237</v>
       </c>
       <c r="B175" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>135362238</v>
       </c>
       <c r="B176" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>135362239</v>
       </c>
       <c r="B177" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>135362240</v>
       </c>
       <c r="B178" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>135362241</v>
       </c>
       <c r="B179" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>135362244</v>
       </c>
       <c r="B180" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>135362245</v>
       </c>
       <c r="B181" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>135362246</v>
       </c>
       <c r="B182" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>135362247</v>
       </c>
       <c r="B183" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>135363842</v>
       </c>
       <c r="B184" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>135363846</v>
       </c>
       <c r="B185" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>135369259</v>
       </c>
       <c r="B186" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>135369266</v>
       </c>
       <c r="B187" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>135369273</v>
       </c>
       <c r="B188" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>135369277</v>
       </c>
       <c r="B189" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>135369278</v>
       </c>
       <c r="B190" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>135357524</v>
       </c>
       <c r="B191" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>135358910</v>
       </c>
       <c r="B192" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>135356934</v>
       </c>
       <c r="B193" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>135356935</v>
       </c>
       <c r="B194" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>135356950</v>
       </c>
       <c r="B195" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>135357244</v>
       </c>
       <c r="B196" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>135357523</v>
       </c>
       <c r="B197" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>135358862</v>
       </c>
       <c r="B198" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>135369265</v>
       </c>
       <c r="B199" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
@@ -23678,7 +23678,7 @@
         <v>135521443</v>
       </c>
       <c r="B200" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>135358512</v>
       </c>
       <c r="B201" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>135358890</v>
       </c>
       <c r="B202" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>135358896</v>
       </c>
       <c r="B203" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>135358898</v>
       </c>
       <c r="B204" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>135363839</v>
       </c>
       <c r="B205" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>135363843</v>
       </c>
       <c r="B206" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135363845</v>
       </c>
       <c r="B207" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>135369268</v>
       </c>
       <c r="B208" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Maja Josefsson, Paulina Delin, Linda Nordström, Klas Magnusson, Isak Falk Eliasson, Helen Sterner, Benny Öwre, anders tedeholm, Elin Götmark, Jennica Andersson</t>
+          <t>Maja Josefsson, Jennica Andersson, Elin Götmark, anders tedeholm, Benny Öwre, Helen Sterner, Isak Falk Eliasson, Klas Magnusson, Linda Nordström, Paulina Delin</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
@@ -24772,7 +24772,7 @@
         <v>135369271</v>
       </c>
       <c r="B209" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>135369280</v>
       </c>
       <c r="B210" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>135357249</v>
       </c>
       <c r="B211" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>135358520</v>
       </c>
       <c r="B212" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>135358894</v>
       </c>
       <c r="B213" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>135369269</v>
       </c>
       <c r="B214" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>135357247</v>
       </c>
       <c r="B215" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>135358516</v>
       </c>
       <c r="B216" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>135358868</v>
       </c>
       <c r="B217" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>135358889</v>
       </c>
       <c r="B218" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>135358892</v>
       </c>
       <c r="B219" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>135362208</v>
       </c>
       <c r="B220" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>135362212</v>
       </c>
       <c r="B221" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>135363838</v>
       </c>
       <c r="B222" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>135363844</v>
       </c>
       <c r="B223" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>135369270</v>
       </c>
       <c r="B224" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>135357824</v>
       </c>
       <c r="B225" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>135357829</v>
       </c>
       <c r="B226" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>135357841</v>
       </c>
       <c r="B227" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>135357843</v>
       </c>
       <c r="B228" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>135357845</v>
       </c>
       <c r="B229" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>135358857</v>
       </c>
       <c r="B230" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>135358865</v>
       </c>
       <c r="B231" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>135369279</v>
       </c>
       <c r="B232" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>135357847</v>
       </c>
       <c r="B234" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>135358530</v>
       </c>
       <c r="B235" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>135358916</v>
       </c>
       <c r="B236" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>135358921</v>
       </c>
       <c r="B237" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>135435470</v>
       </c>
       <c r="B238" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>135358529</v>
       </c>
       <c r="B239" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>135362228</v>
       </c>
       <c r="B240" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>135435699</v>
       </c>
       <c r="B242" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>135357260</v>
       </c>
       <c r="B243" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>135363836</v>
       </c>
       <c r="B244" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>135357535</v>
       </c>
       <c r="B245" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>135358514</v>
       </c>
       <c r="B246" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>135358537</v>
       </c>
       <c r="B247" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>135363837</v>
       </c>
       <c r="B248" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>135363840</v>
       </c>
       <c r="B249" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>135358540</v>
       </c>
       <c r="B250" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>135357257</v>
       </c>
       <c r="B251" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>135357530</v>
       </c>
       <c r="B252" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>135358927</v>
       </c>
       <c r="B253" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>135362203</v>
       </c>
       <c r="B254" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>135362223</v>
       </c>
       <c r="B255" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>135363849</v>
       </c>
       <c r="B256" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>135363851</v>
       </c>
       <c r="B257" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>135357533</v>
       </c>
       <c r="B258" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>135358926</v>
       </c>
       <c r="B259" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>135358920</v>
       </c>
       <c r="B260" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>135521161</v>
       </c>
       <c r="B261" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>135358863</v>
       </c>
       <c r="B262" t="n">
-        <v>95840</v>
+        <v>95884</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135358925</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135363850</v>
       </c>
       <c r="B3" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>135357256</v>
       </c>
       <c r="B4" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>135357527</v>
       </c>
       <c r="B5" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>135357531</v>
       </c>
       <c r="B6" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>135357538</v>
       </c>
       <c r="B7" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>135363848</v>
       </c>
       <c r="B8" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135362202</v>
       </c>
       <c r="B9" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135356943</v>
       </c>
       <c r="B10" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>135357830</v>
       </c>
       <c r="B11" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135520047</v>
       </c>
       <c r="B12" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135356953</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135357254</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135357258</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135357261</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>135357540</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>135357543</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>135357825</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135357837</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>135357842</v>
       </c>
       <c r="B21" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135358539</v>
       </c>
       <c r="B22" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135358870</v>
       </c>
       <c r="B23" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135358879</v>
       </c>
       <c r="B24" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135358883</v>
       </c>
       <c r="B25" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135358885</v>
       </c>
       <c r="B26" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135358923</v>
       </c>
       <c r="B27" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135362243</v>
       </c>
       <c r="B28" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>135369274</v>
       </c>
       <c r="B29" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>135363841</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>135357838</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>135312324</v>
       </c>
       <c r="B52" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>135357823</v>
       </c>
       <c r="B53" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>135357835</v>
       </c>
       <c r="B54" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>135358881</v>
       </c>
       <c r="B55" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>135362216</v>
       </c>
       <c r="B56" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>135357255</v>
       </c>
       <c r="B57" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>135357828</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>135358867</v>
       </c>
       <c r="B59" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>135358919</v>
       </c>
       <c r="B60" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>135358922</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>135362204</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>135356949</v>
       </c>
       <c r="B63" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>135357827</v>
       </c>
       <c r="B64" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>135357831</v>
       </c>
       <c r="B65" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>135357844</v>
       </c>
       <c r="B66" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>135357846</v>
       </c>
       <c r="B67" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135363847</v>
       </c>
       <c r="B68" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135357826</v>
       </c>
       <c r="B82" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>135357539</v>
       </c>
       <c r="B86" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>135435690</v>
       </c>
       <c r="B87" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135435692</v>
       </c>
       <c r="B88" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>135356945</v>
       </c>
       <c r="B89" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>135356947</v>
       </c>
       <c r="B90" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>135357260</v>
       </c>
       <c r="B243" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>135363836</v>
       </c>
       <c r="B244" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>135357535</v>
       </c>
       <c r="B245" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>135358514</v>
       </c>
       <c r="B246" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>135358537</v>
       </c>
       <c r="B247" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>135363837</v>
       </c>
       <c r="B248" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>135363840</v>
       </c>
       <c r="B249" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>135358540</v>
       </c>
       <c r="B250" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>135357257</v>
       </c>
       <c r="B251" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>135357530</v>
       </c>
       <c r="B252" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>135358927</v>
       </c>
       <c r="B253" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>135362203</v>
       </c>
       <c r="B254" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>135362223</v>
       </c>
       <c r="B255" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>135363849</v>
       </c>
       <c r="B256" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>135363851</v>
       </c>
       <c r="B257" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>135357533</v>
       </c>
       <c r="B258" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>135358926</v>
       </c>
       <c r="B259" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>135358863</v>
       </c>
       <c r="B262" t="n">
-        <v>95916</v>
+        <v>95918</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>135363850</v>
       </c>
       <c r="B3" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>135363848</v>
       </c>
       <c r="B8" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135520047</v>
       </c>
       <c r="B12" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135358539</v>
       </c>
       <c r="B22" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>135363841</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>92637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>135358523</v>
       </c>
       <c r="B34" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>135358526</v>
       </c>
       <c r="B35" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>135358534</v>
       </c>
       <c r="B37" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>135363847</v>
       </c>
       <c r="B68" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>135358513</v>
       </c>
       <c r="B84" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>135435690</v>
       </c>
       <c r="B87" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>135435692</v>
       </c>
       <c r="B88" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>135358506</v>
       </c>
       <c r="B126" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>135363842</v>
       </c>
       <c r="B184" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>135363846</v>
       </c>
       <c r="B185" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>135521443</v>
       </c>
       <c r="B200" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>135358512</v>
       </c>
       <c r="B201" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>135363839</v>
       </c>
       <c r="B205" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>135363843</v>
       </c>
       <c r="B206" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>135363845</v>
       </c>
       <c r="B207" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>135358520</v>
       </c>
       <c r="B212" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>135358516</v>
       </c>
       <c r="B216" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>135363838</v>
       </c>
       <c r="B222" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>135363844</v>
       </c>
       <c r="B223" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>135435470</v>
       </c>
       <c r="B238" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>135435699</v>
       </c>
       <c r="B242" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>135363836</v>
       </c>
       <c r="B244" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>135358514</v>
       </c>
       <c r="B246" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>135363837</v>
       </c>
       <c r="B248" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>135363840</v>
       </c>
       <c r="B249" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>135358540</v>
       </c>
       <c r="B250" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>135363849</v>
       </c>
       <c r="B256" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>135363851</v>
       </c>
       <c r="B257" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>135521161</v>
       </c>
       <c r="B261" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1885,7 +1885,7 @@
         <v>135520047</v>
       </c>
       <c r="B12" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135358539</v>
       </c>
       <c r="B22" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>135358523</v>
       </c>
       <c r="B34" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>135358526</v>
       </c>
       <c r="B35" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>135358534</v>
       </c>
       <c r="B37" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>135358513</v>
       </c>
       <c r="B84" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>135358506</v>
       </c>
       <c r="B126" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>135521443</v>
       </c>
       <c r="B200" t="n">
-        <v>80562</v>
+        <v>80563</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>135358512</v>
       </c>
       <c r="B201" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>135358520</v>
       </c>
       <c r="B212" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>135358516</v>
       </c>
       <c r="B216" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>135358514</v>
       </c>
       <c r="B246" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>135358540</v>
       </c>
       <c r="B250" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>135521161</v>
       </c>
       <c r="B261" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>136336944</v>
       </c>
       <c r="B248" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>136336945</v>
       </c>
       <c r="B249" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>136336935</v>
       </c>
       <c r="B257" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>136336931</v>
       </c>
       <c r="B287" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136336939</v>
       </c>
       <c r="B288" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>136336948</v>
       </c>
       <c r="B289" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>136336954</v>
       </c>
       <c r="B290" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>136336960</v>
       </c>
       <c r="B291" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>136336965</v>
       </c>
       <c r="B292" t="n">
-        <v>78463</v>
+        <v>78469</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>136336944</v>
       </c>
       <c r="B248" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>136336945</v>
       </c>
       <c r="B249" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>136336935</v>
       </c>
       <c r="B257" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>136336931</v>
       </c>
       <c r="B287" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136336939</v>
       </c>
       <c r="B288" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>136336948</v>
       </c>
       <c r="B289" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>136336954</v>
       </c>
       <c r="B290" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>136336960</v>
       </c>
       <c r="B291" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>136336965</v>
       </c>
       <c r="B292" t="n">
-        <v>78469</v>
+        <v>78482</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>

--- a/artfynd/A 26053-2026 artfynd.xlsx
+++ b/artfynd/A 26053-2026 artfynd.xlsx
@@ -1656,7 +1656,7 @@
         <v>136336934</v>
       </c>
       <c r="B10" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>136336942</v>
       </c>
       <c r="B52" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136336929</v>
       </c>
       <c r="B193" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136336930</v>
       </c>
       <c r="B194" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136336936</v>
       </c>
       <c r="B195" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136336937</v>
       </c>
       <c r="B196" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136336938</v>
       </c>
       <c r="B197" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>136336943</v>
       </c>
       <c r="B198" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>136336947</v>
       </c>
       <c r="B199" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136336949</v>
       </c>
       <c r="B200" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136336950</v>
       </c>
       <c r="B201" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>136336951</v>
       </c>
       <c r="B202" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>136336955</v>
       </c>
       <c r="B203" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>136336958</v>
       </c>
       <c r="B204" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>136336961</v>
       </c>
       <c r="B205" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>136336963</v>
       </c>
       <c r="B206" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>136336964</v>
       </c>
       <c r="B207" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>136336968</v>
       </c>
       <c r="B208" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>136336940</v>
       </c>
       <c r="B218" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>136336952</v>
       </c>
       <c r="B219" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>136336959</v>
       </c>
       <c r="B220" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>136336932</v>
       </c>
       <c r="B221" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>136336956</v>
       </c>
       <c r="B222" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -33555,7 +33555,7 @@
         <v>136336941</v>
       </c>
       <c r="B284" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>136336931</v>
       </c>
       <c r="B287" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136336939</v>
       </c>
       <c r="B288" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>136336948</v>
       </c>
       <c r="B289" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>136336954</v>
       </c>
       <c r="B290" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>136336960</v>
       </c>
       <c r="B291" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>136336965</v>
       </c>
       <c r="B292" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
